--- a/site/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/headings.xlsx
+++ b/site/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -627,12 +627,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KBCXNWMVYC5G2CZ1T6QN1TXB</t>
+          <t>h_01KHTN0SGKTY5RGQTV6Y86FEXV</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KBCXNWMVYC5G2CZ1T6QN1TXB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KHTN0SGKTY5RGQTV6Y86FEXV</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Execution Settings</t>
+          <t>Manage Workers</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,41 +671,41 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KBCZB76XV5N2RY0CEQVD139J</t>
+          <t>h_01KBES1SN0BST02WTHB0X59H4A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KBCZB76XV5N2RY0CEQVD139J</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KBES1SN0BST02WTHB0X59H4A</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Manage Workers</t>
+          <t>Correlations and Filters</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KBES1SN0BST02WTHB0X59H4A</t>
+          <t>h_01KBD03PNFQS9P6T0XRE8AGSR3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KBES1SN0BST02WTHB0X59H4A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KBD03PNFQS9P6T0XRE8AGSR3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Correlations and Filters</t>
+          <t>Update Worker</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KBD03PNFQS9P6T0XRE8AGSR3</t>
+          <t>h_01KBERW57JPNDEGV7F732G6BEQ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KBD03PNFQS9P6T0XRE8AGSR3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KBERW57JPNDEGV7F732G6BEQ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Update Worker</t>
+          <t>Manage Candidates</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,41 +737,41 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KBERW57JPNDEGV7F732G6BEQ</t>
+          <t>h_01KBES2DKDXJ2J4NV76YE4TVHE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KBERW57JPNDEGV7F732G6BEQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KBES2DKDXJ2J4NV76YE4TVHE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Manage Candidates</t>
+          <t>Writeback to ADP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KBES2DKDXJ2J4NV76YE4TVHE</t>
+          <t>h_01KHX85GGKNWFB1HQZ1KRFVGEX</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KBES2DKDXJ2J4NV76YE4TVHE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KHX85GGKNWFB1HQZ1KRFVGEX</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Active Directory Group Assignment</t>
+          <t>Deprovisioning Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KC102VB2RE2246G5FZ1QSJSM</t>
+          <t>h_01KHX8BJYE9BM8PBT433M7P41X</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KC102VB2RE2246G5FZ1QSJSM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KHX8BJYE9BM8PBT433M7P41X</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EntraID Group Management</t>
+          <t>Active Directory Group Assignment</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KC143Y4H5PD3NDP77H96PPWE</t>
+          <t>h_01KHX86Y0TYGWM5GYJFNJYM37E</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KC143Y4H5PD3NDP77H96PPWE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KHX86Y0TYGWM5GYJFNJYM37E</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Update User</t>
+          <t>EntraID Group Management</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KC1ESTVV12GGSYFYF1TVQD0M</t>
+          <t>h_01KC143Y4H5PD3NDP77H96PPWE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KC1ESTVV12GGSYFYF1TVQD0M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KC143Y4H5PD3NDP77H96PPWE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Password Policy Settings</t>
+          <t>Update User</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KC1GM7JZVM56KVVB0AW08EWW</t>
+          <t>h_01KJ466YCS4AXS6FNK7RNYA84X</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KC1GM7JZVM56KVVB0AW08EWW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KJ466YCS4AXS6FNK7RNYA84X</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Password Policy Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KF2KTKDW02D8KAXNH46THQKH</t>
+          <t>h_01KC1GM7JZVM56KVVB0AW08EWW</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF2KTKDW02D8KAXNH46THQKH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KC1GM7JZVM56KVVB0AW08EWW</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Naming Policy Settings</t>
+          <t>Debug Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,41 +891,41 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KC3DJWXP3PP4H5JRT6CCV8Z8</t>
+          <t>h_01KF2KTKDW02D8KAXNH46THQKH</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KC3DJWXP3PP4H5JRT6CCV8Z8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF2KTKDW02D8KAXNH46THQKH</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Generate sAMAccountName</t>
+          <t>Naming Policy Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KF35CN3A1XQ0PP3DZHTQGG0R</t>
+          <t>h_01KJ4BM04W5QGGPRCTQVP0C5A8</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF35CN3A1XQ0PP3DZHTQGG0R</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KJ4BM04W5QGGPRCTQVP0C5A8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Generate Common Name (CN)</t>
+          <t>Generate sAMAccountName</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KF2NC2X1F05GBSTZX9YNNVQT</t>
+          <t>h_01KF35CN3A1XQ0PP3DZHTQGG0R</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF2NC2X1F05GBSTZX9YNNVQT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF35CN3A1XQ0PP3DZHTQGG0R</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Generate Proxy Address</t>
+          <t>Generate Common Name (CN)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,41 +957,41 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KF2SS6P6HV2H2DSXX5Y55NJJ</t>
+          <t>h_01KF2NC2X1F05GBSTZX9YNNVQT</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF2SS6P6HV2H2DSXX5Y55NJJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF2NC2X1F05GBSTZX9YNNVQT</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Generate Proxy Address</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KF2SYFHS5XE0V3VPDKBK9Z3C</t>
+          <t>h_01KF2SS6P6HV2H2DSXX5Y55NJJ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF2SYFHS5XE0V3VPDKBK9Z3C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF2SS6P6HV2H2DSXX5Y55NJJ</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,41 +1001,41 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KC5YKDMWPXWYS4J9GSRAYWRS</t>
+          <t>h_01KJ4ABHTNQV51DQMB6EB3N6DZ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KC5YKDMWPXWYS4J9GSRAYWRS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KJ4ABHTNQV51DQMB6EB3N6DZ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KF35GDEN08FE4757TPWBZZ9P</t>
+          <t>h_01KC5YKDMWPXWYS4J9GSRAYWRS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF35GDEN08FE4757TPWBZZ9P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KC5YKDMWPXWYS4J9GSRAYWRS</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,41 +1045,41 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KC621XWV4P9MTHMNNVZFG354</t>
+          <t>h_01KJ4AC1GWTBGV65FZ8STG9R7J</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KC621XWV4P9MTHMNNVZFG354</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KJ4AC1GWTBGV65FZ8STG9R7J</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Candidate Group Assignment Rules</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KF30N1HFTDRY8CRX479A2R78</t>
+          <t>h_01KC621XWV4P9MTHMNNVZFG354</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF30N1HFTDRY8CRX479A2R78</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KC621XWV4P9MTHMNNVZFG354</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AD Candidate Group Rules</t>
+          <t>Candidate Group Assignment Rules</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,19 +1089,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KF35KQ54CQCWFPC23Y7DAP11</t>
+          <t>h_01KF30N1HFTDRY8CRX479A2R78</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF35KQ54CQCWFPC23Y7DAP11</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF30N1HFTDRY8CRX479A2R78</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Entra Candidate Group Rules</t>
+          <t>AD Candidate Group Rules</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,19 +1111,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KF35KQ55972CGKDRX6CQPDZR</t>
+          <t>h_01KF35KQ54CQCWFPC23Y7DAP11</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF35KQ55972CGKDRX6CQPDZR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF35KQ54CQCWFPC23Y7DAP11</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Worker Group Assignment Rules</t>
+          <t>Entra Candidate Group Rules</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,19 +1133,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KF35KQ58CPAV4B5DNVPJ84Q2</t>
+          <t>h_01KF35KQ55972CGKDRX6CQPDZR</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF35KQ58CPAV4B5DNVPJ84Q2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF35KQ55972CGKDRX6CQPDZR</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AD Worker Group Rules</t>
+          <t>Worker Group Assignment Rules</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1155,19 +1155,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01KF35KQ585YWBFNZ0J3870FCN</t>
+          <t>h_01KF35KQ58CPAV4B5DNVPJ84Q2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF35KQ585YWBFNZ0J3870FCN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF35KQ58CPAV4B5DNVPJ84Q2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Entra Worker Group Rules</t>
+          <t>AD Worker Group Rules</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1177,19 +1177,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01KF35KQ5A94M4RV0VH9R1CBM8</t>
+          <t>h_01KF35KQ585YWBFNZ0J3870FCN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF35KQ5A94M4RV0VH9R1CBM8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF35KQ585YWBFNZ0J3870FCN</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Active Directory OU Rules</t>
+          <t>Entra Worker Group Rules</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1199,19 +1199,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01KF35KQ5BEHN5HXF0K10PJT7T</t>
+          <t>h_01KF35KQ5A94M4RV0VH9R1CBM8</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF35KQ5BEHN5HXF0K10PJT7T</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF35KQ5A94M4RV0VH9R1CBM8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Rule Behavior</t>
+          <t>Active Directory OU Rules</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1221,164 +1221,208 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01KF35KQ5C8D0WS7X2BANT4CNV</t>
+          <t>h_01KF35KQ5BEHN5HXF0K10PJT7T</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF35KQ5C8D0WS7X2BANT4CNV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF35KQ5BEHN5HXF0K10PJT7T</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>License Management Rules</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01KF353V9MQRK8PSJR60C5M9DN</t>
+          <t>h_01KJ477RVTFE61J9YSD18W0H86</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF353V9MQRK8PSJR60C5M9DN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KJ477RVTFE61J9YSD18W0H86</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Rule Behavior</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01KF353SX36HM336G2107Q3Z7P</t>
+          <t>h_01KJ479Q2EYXYV01ABR18K6ZGF</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF353SX36HM336G2107Q3Z7P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KJ479Q2EYXYV01ABR18K6ZGF</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Active Directory User Email Domain Table</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01KF35850PGYTFGBXNJNBJ2EPF</t>
+          <t>h_01KF353V9MQRK8PSJR60C5M9DN</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF35850PGYTFGBXNJNBJ2EPF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF353V9MQRK8PSJR60C5M9DN</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Candidate Emails to Ignore</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>h_01KF358YPVJ75VPZKAPA2MWGAC</t>
+          <t>h_01KF353SX36HM336G2107Q3Z7P</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF358YPVJ75VPZKAPA2MWGAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF353SX36HM336G2107Q3Z7P</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Active Directory User Email Domain Table</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>h_01KF359K4PMY6TFXA4V9GYVYJJ</t>
+          <t>h_01KF35850PGYTFGBXNJNBJ2EPF</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF359K4PMY6TFXA4V9GYVYJJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF35850PGYTFGBXNJNBJ2EPF</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Candidate Emails to Ignore</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KF358YPVJ75VPZKAPA2MWGAC</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF358YPVJ75VPZKAPA2MWGAC</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>h_01KF359K4PMY6TFXA4V9GYVYJJ</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KF359K4PMY6TFXA4V9GYVYJJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/headings.xlsx
+++ b/site/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/headings.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KBD03PNFQS9P6T0XRE8AGSR3</t>
+          <t>h_01KJ9JFHHZFM4VHK4TNRB7V32T</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KBD03PNFQS9P6T0XRE8AGSR3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Active-Directory-and-Entra-ID-Lifecycle-Integration/#h_01KJ9JFHHZFM4VHK4TNRB7V32T</t>
         </is>
       </c>
     </row>
